--- a/Data/Rules/Colorado Pet Treats Rules Matrix.xlsx
+++ b/Data/Rules/Colorado Pet Treats Rules Matrix.xlsx
@@ -742,10 +742,10 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -763,7 +763,7 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z2" t="b">
         <v>0</v>
@@ -778,10 +778,10 @@
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF2" t="b">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" t="b">
         <v>0</v>
@@ -864,10 +864,10 @@
         <v>0</v>
       </c>
       <c r="R3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -885,7 +885,7 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z3" t="b">
         <v>0</v>
@@ -900,10 +900,10 @@
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF3" t="b">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>2</v>
       </c>
       <c r="S4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -1007,7 +1007,7 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z4" t="b">
         <v>0</v>
@@ -1081,10 +1081,10 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
@@ -1111,7 +1111,7 @@
         <v>2</v>
       </c>
       <c r="S5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -1129,7 +1129,7 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z5" t="b">
         <v>0</v>
@@ -1230,10 +1230,10 @@
         <v>0</v>
       </c>
       <c r="R6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -1251,7 +1251,7 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z6" t="b">
         <v>0</v>
@@ -1266,10 +1266,10 @@
         <v>0</v>
       </c>
       <c r="AD6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF6" t="b">
         <v>0</v>
@@ -1325,10 +1325,10 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7" t="b">
         <v>0</v>
@@ -1352,10 +1352,10 @@
         <v>0</v>
       </c>
       <c r="R7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z7" t="b">
         <v>0</v>
@@ -1388,10 +1388,10 @@
         <v>0</v>
       </c>
       <c r="AD7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF7" t="b">
         <v>0</v>
@@ -1474,10 +1474,10 @@
         <v>0</v>
       </c>
       <c r="R8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z8" t="b">
         <v>0</v>
@@ -1510,10 +1510,10 @@
         <v>0</v>
       </c>
       <c r="AD8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF8" t="b">
         <v>0</v>
@@ -1596,10 +1596,10 @@
         <v>0</v>
       </c>
       <c r="R9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S9">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -1617,7 +1617,7 @@
         <v>2</v>
       </c>
       <c r="Y9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z9" t="b">
         <v>0</v>
@@ -1632,10 +1632,10 @@
         <v>0</v>
       </c>
       <c r="AD9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF9" t="b">
         <v>0</v>
@@ -1721,7 +1721,7 @@
         <v>2</v>
       </c>
       <c r="S10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -1739,7 +1739,7 @@
         <v>2</v>
       </c>
       <c r="Y10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z10" t="b">
         <v>0</v>
@@ -1813,10 +1813,10 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
@@ -1843,7 +1843,7 @@
         <v>2</v>
       </c>
       <c r="S11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T11" t="b">
         <v>0</v>
@@ -1861,7 +1861,7 @@
         <v>2</v>
       </c>
       <c r="Y11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z11" t="b">
         <v>0</v>
@@ -1935,10 +1935,10 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
@@ -1965,7 +1965,7 @@
         <v>2</v>
       </c>
       <c r="S12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T12" t="b">
         <v>0</v>
@@ -1983,7 +1983,7 @@
         <v>2</v>
       </c>
       <c r="Y12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z12" t="b">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="AD12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF12" t="b">
         <v>0</v>
@@ -2057,10 +2057,10 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
@@ -2087,7 +2087,7 @@
         <v>2</v>
       </c>
       <c r="S13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T13" t="b">
         <v>0</v>
@@ -2105,7 +2105,7 @@
         <v>2</v>
       </c>
       <c r="Y13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z13" t="b">
         <v>0</v>
@@ -2179,10 +2179,10 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14" t="b">
         <v>0</v>
@@ -2209,7 +2209,7 @@
         <v>2</v>
       </c>
       <c r="S14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T14" t="b">
         <v>0</v>
@@ -2227,7 +2227,7 @@
         <v>2</v>
       </c>
       <c r="Y14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z14" t="b">
         <v>0</v>
@@ -2301,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
@@ -2331,7 +2331,7 @@
         <v>2</v>
       </c>
       <c r="S15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T15" t="b">
         <v>0</v>
@@ -2349,7 +2349,7 @@
         <v>2</v>
       </c>
       <c r="Y15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z15" t="b">
         <v>0</v>
@@ -2423,10 +2423,10 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K16" t="b">
         <v>0</v>
@@ -2453,7 +2453,7 @@
         <v>2</v>
       </c>
       <c r="S16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T16" t="b">
         <v>0</v>
@@ -2471,7 +2471,7 @@
         <v>2</v>
       </c>
       <c r="Y16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z16" t="b">
         <v>0</v>
@@ -2545,10 +2545,10 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K17" t="b">
         <v>0</v>
@@ -2569,13 +2569,13 @@
         <v>2</v>
       </c>
       <c r="Q17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T17" t="b">
         <v>0</v>
@@ -2593,7 +2593,7 @@
         <v>2</v>
       </c>
       <c r="Y17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z17" t="b">
         <v>0</v>
@@ -2605,13 +2605,13 @@
         <v>2</v>
       </c>
       <c r="AC17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="b">
         <v>0</v>

--- a/Data/Rules/Colorado Pet Treats Rules Matrix.xlsx
+++ b/Data/Rules/Colorado Pet Treats Rules Matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="75">
   <si>
     <t>SKU</t>
   </si>
@@ -134,6 +134,12 @@
   </si>
   <si>
     <t>HQ_Max</t>
+  </si>
+  <si>
+    <t>TMAX</t>
+  </si>
+  <si>
+    <t>Total Max</t>
   </si>
   <si>
     <t>12117</t>
@@ -564,10 +570,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AN17"/>
+  <dimension ref="A1:AP17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:40">
+    <row r="1" spans="1:42">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -688,16 +694,22 @@
       <c r="AN1" t="s">
         <v>39</v>
       </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>41</v>
+      </c>
     </row>
-    <row r="2" spans="1:40">
+    <row r="2" spans="1:42">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -810,16 +822,22 @@
       <c r="AN2">
         <v>0</v>
       </c>
+      <c r="AO2">
+        <v>48</v>
+      </c>
+      <c r="AP2">
+        <v>34</v>
+      </c>
     </row>
-    <row r="3" spans="1:40">
+    <row r="3" spans="1:42">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -873,10 +891,10 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W3" t="b">
         <v>0</v>
@@ -932,16 +950,22 @@
       <c r="AN3">
         <v>0</v>
       </c>
+      <c r="AO3">
+        <v>52</v>
+      </c>
+      <c r="AP3">
+        <v>37</v>
+      </c>
     </row>
-    <row r="4" spans="1:40">
+    <row r="4" spans="1:42">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1054,138 +1078,150 @@
       <c r="AN4">
         <v>0</v>
       </c>
+      <c r="AO4">
+        <v>40</v>
+      </c>
+      <c r="AP4">
+        <v>30</v>
+      </c>
     </row>
-    <row r="5" spans="1:40">
+    <row r="5" spans="1:42">
       <c r="A5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>2</v>
+      </c>
+      <c r="S5">
+        <v>4</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>3</v>
+      </c>
+      <c r="V5">
+        <v>4</v>
+      </c>
+      <c r="W5" t="b">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>2</v>
+      </c>
+      <c r="Y5">
+        <v>4</v>
+      </c>
+      <c r="Z5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
+      <c r="AB5">
+        <v>2</v>
+      </c>
+      <c r="AC5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>2</v>
+      </c>
+      <c r="AE5">
+        <v>3</v>
+      </c>
+      <c r="AF5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>2</v>
+      </c>
+      <c r="AH5">
+        <v>3</v>
+      </c>
+      <c r="AI5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>1</v>
+      </c>
+      <c r="AK5">
+        <v>2</v>
+      </c>
+      <c r="AL5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
         <v>43</v>
       </c>
-      <c r="B5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>3</v>
-      </c>
-      <c r="N5" t="b">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>1</v>
-      </c>
-      <c r="P5">
-        <v>2</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>2</v>
-      </c>
-      <c r="S5">
-        <v>4</v>
-      </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>2</v>
-      </c>
-      <c r="V5">
-        <v>3</v>
-      </c>
-      <c r="W5" t="b">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <v>2</v>
-      </c>
-      <c r="Y5">
-        <v>4</v>
-      </c>
-      <c r="Z5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA5">
-        <v>1</v>
-      </c>
-      <c r="AB5">
-        <v>2</v>
-      </c>
-      <c r="AC5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>2</v>
-      </c>
-      <c r="AE5">
-        <v>3</v>
-      </c>
-      <c r="AF5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5">
-        <v>2</v>
-      </c>
-      <c r="AH5">
-        <v>3</v>
-      </c>
-      <c r="AI5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ5">
-        <v>1</v>
-      </c>
-      <c r="AK5">
-        <v>2</v>
-      </c>
-      <c r="AL5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>0</v>
+      <c r="AP5">
+        <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:40">
+    <row r="6" spans="1:42">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1239,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W6" t="b">
         <v>0</v>
@@ -1298,16 +1334,22 @@
       <c r="AN6">
         <v>0</v>
       </c>
+      <c r="AO6">
+        <v>49</v>
+      </c>
+      <c r="AP6">
+        <v>35</v>
+      </c>
     </row>
-    <row r="7" spans="1:40">
+    <row r="7" spans="1:42">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1420,16 +1462,22 @@
       <c r="AN7">
         <v>0</v>
       </c>
+      <c r="AO7">
+        <v>51</v>
+      </c>
+      <c r="AP7">
+        <v>36</v>
+      </c>
     </row>
-    <row r="8" spans="1:40">
+    <row r="8" spans="1:42">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1542,16 +1590,22 @@
       <c r="AN8">
         <v>0</v>
       </c>
+      <c r="AO8">
+        <v>49</v>
+      </c>
+      <c r="AP8">
+        <v>35</v>
+      </c>
     </row>
-    <row r="9" spans="1:40">
+    <row r="9" spans="1:42">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1664,16 +1718,22 @@
       <c r="AN9">
         <v>0</v>
       </c>
+      <c r="AO9">
+        <v>51</v>
+      </c>
+      <c r="AP9">
+        <v>36</v>
+      </c>
     </row>
-    <row r="10" spans="1:40">
+    <row r="10" spans="1:42">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1727,10 +1787,10 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W10" t="b">
         <v>0</v>
@@ -1786,16 +1846,22 @@
       <c r="AN10">
         <v>0</v>
       </c>
+      <c r="AO10">
+        <v>41</v>
+      </c>
+      <c r="AP10">
+        <v>31</v>
+      </c>
     </row>
-    <row r="11" spans="1:40">
+    <row r="11" spans="1:42">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1908,16 +1974,22 @@
       <c r="AN11">
         <v>0</v>
       </c>
+      <c r="AO11">
+        <v>42</v>
+      </c>
+      <c r="AP11">
+        <v>31</v>
+      </c>
     </row>
-    <row r="12" spans="1:40">
+    <row r="12" spans="1:42">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -2030,504 +2102,534 @@
       <c r="AN12">
         <v>0</v>
       </c>
+      <c r="AO12">
+        <v>44</v>
+      </c>
+      <c r="AP12">
+        <v>33</v>
+      </c>
     </row>
-    <row r="13" spans="1:40">
+    <row r="13" spans="1:42">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
+      </c>
+      <c r="J13">
+        <v>3</v>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>2</v>
+      </c>
+      <c r="M13">
+        <v>3</v>
+      </c>
+      <c r="N13" t="b">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="b">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>2</v>
+      </c>
+      <c r="S13">
+        <v>4</v>
+      </c>
+      <c r="T13" t="b">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>2</v>
+      </c>
+      <c r="V13">
+        <v>3</v>
+      </c>
+      <c r="W13" t="b">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>2</v>
+      </c>
+      <c r="Y13">
+        <v>4</v>
+      </c>
+      <c r="Z13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>1</v>
+      </c>
+      <c r="AB13">
+        <v>2</v>
+      </c>
+      <c r="AC13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>2</v>
+      </c>
+      <c r="AE13">
+        <v>3</v>
+      </c>
+      <c r="AF13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>2</v>
+      </c>
+      <c r="AH13">
+        <v>3</v>
+      </c>
+      <c r="AI13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>1</v>
+      </c>
+      <c r="AK13">
+        <v>2</v>
+      </c>
+      <c r="AL13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>42</v>
+      </c>
+      <c r="AP13">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:42">
+      <c r="A14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
+      </c>
+      <c r="J14">
+        <v>3</v>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>2</v>
+      </c>
+      <c r="M14">
+        <v>3</v>
+      </c>
+      <c r="N14" t="b">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>2</v>
+      </c>
+      <c r="S14">
+        <v>4</v>
+      </c>
+      <c r="T14" t="b">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>2</v>
+      </c>
+      <c r="V14">
+        <v>3</v>
+      </c>
+      <c r="W14" t="b">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>2</v>
+      </c>
+      <c r="Y14">
+        <v>4</v>
+      </c>
+      <c r="Z14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>1</v>
+      </c>
+      <c r="AB14">
+        <v>2</v>
+      </c>
+      <c r="AC14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>2</v>
+      </c>
+      <c r="AE14">
+        <v>3</v>
+      </c>
+      <c r="AF14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>2</v>
+      </c>
+      <c r="AH14">
+        <v>3</v>
+      </c>
+      <c r="AI14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>1</v>
+      </c>
+      <c r="AK14">
+        <v>2</v>
+      </c>
+      <c r="AL14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>42</v>
+      </c>
+      <c r="AP14">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:42">
+      <c r="A15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>2</v>
+      </c>
+      <c r="J15">
+        <v>3</v>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>2</v>
+      </c>
+      <c r="M15">
+        <v>3</v>
+      </c>
+      <c r="N15" t="b">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="b">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>2</v>
+      </c>
+      <c r="S15">
+        <v>4</v>
+      </c>
+      <c r="T15" t="b">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>2</v>
+      </c>
+      <c r="V15">
+        <v>3</v>
+      </c>
+      <c r="W15" t="b">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>2</v>
+      </c>
+      <c r="Y15">
+        <v>4</v>
+      </c>
+      <c r="Z15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>1</v>
+      </c>
+      <c r="AB15">
+        <v>2</v>
+      </c>
+      <c r="AC15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>2</v>
+      </c>
+      <c r="AE15">
+        <v>3</v>
+      </c>
+      <c r="AF15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>2</v>
+      </c>
+      <c r="AH15">
+        <v>3</v>
+      </c>
+      <c r="AI15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>1</v>
+      </c>
+      <c r="AK15">
+        <v>2</v>
+      </c>
+      <c r="AL15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>42</v>
+      </c>
+      <c r="AP15">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:42">
+      <c r="A16" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" t="s">
         <v>72</v>
       </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>2</v>
-      </c>
-      <c r="J13">
-        <v>3</v>
-      </c>
-      <c r="K13" t="b">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>2</v>
-      </c>
-      <c r="M13">
-        <v>3</v>
-      </c>
-      <c r="N13" t="b">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>1</v>
-      </c>
-      <c r="P13">
-        <v>2</v>
-      </c>
-      <c r="Q13" t="b">
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <v>2</v>
-      </c>
-      <c r="S13">
-        <v>4</v>
-      </c>
-      <c r="T13" t="b">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>2</v>
-      </c>
-      <c r="V13">
-        <v>3</v>
-      </c>
-      <c r="W13" t="b">
-        <v>0</v>
-      </c>
-      <c r="X13">
-        <v>2</v>
-      </c>
-      <c r="Y13">
-        <v>4</v>
-      </c>
-      <c r="Z13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA13">
-        <v>1</v>
-      </c>
-      <c r="AB13">
-        <v>2</v>
-      </c>
-      <c r="AC13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD13">
-        <v>2</v>
-      </c>
-      <c r="AE13">
-        <v>3</v>
-      </c>
-      <c r="AF13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13">
-        <v>2</v>
-      </c>
-      <c r="AH13">
-        <v>3</v>
-      </c>
-      <c r="AI13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ13">
-        <v>1</v>
-      </c>
-      <c r="AK13">
-        <v>2</v>
-      </c>
-      <c r="AL13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>0</v>
+      <c r="C16" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>2</v>
+      </c>
+      <c r="J16">
+        <v>3</v>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>2</v>
+      </c>
+      <c r="M16">
+        <v>3</v>
+      </c>
+      <c r="N16" t="b">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>2</v>
+      </c>
+      <c r="S16">
+        <v>4</v>
+      </c>
+      <c r="T16" t="b">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>2</v>
+      </c>
+      <c r="V16">
+        <v>3</v>
+      </c>
+      <c r="W16" t="b">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>2</v>
+      </c>
+      <c r="Y16">
+        <v>4</v>
+      </c>
+      <c r="Z16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>1</v>
+      </c>
+      <c r="AB16">
+        <v>2</v>
+      </c>
+      <c r="AC16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>2</v>
+      </c>
+      <c r="AE16">
+        <v>3</v>
+      </c>
+      <c r="AF16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>2</v>
+      </c>
+      <c r="AH16">
+        <v>3</v>
+      </c>
+      <c r="AI16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>1</v>
+      </c>
+      <c r="AK16">
+        <v>2</v>
+      </c>
+      <c r="AL16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>42</v>
+      </c>
+      <c r="AP16">
+        <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:40">
-      <c r="A14" t="s">
-        <v>52</v>
-      </c>
-      <c r="B14" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" t="s">
-        <v>72</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-      <c r="H14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>2</v>
-      </c>
-      <c r="J14">
-        <v>3</v>
-      </c>
-      <c r="K14" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>2</v>
-      </c>
-      <c r="M14">
-        <v>3</v>
-      </c>
-      <c r="N14" t="b">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>1</v>
-      </c>
-      <c r="P14">
-        <v>2</v>
-      </c>
-      <c r="Q14" t="b">
-        <v>0</v>
-      </c>
-      <c r="R14">
-        <v>2</v>
-      </c>
-      <c r="S14">
-        <v>4</v>
-      </c>
-      <c r="T14" t="b">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>2</v>
-      </c>
-      <c r="V14">
-        <v>3</v>
-      </c>
-      <c r="W14" t="b">
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <v>2</v>
-      </c>
-      <c r="Y14">
-        <v>4</v>
-      </c>
-      <c r="Z14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA14">
-        <v>1</v>
-      </c>
-      <c r="AB14">
-        <v>2</v>
-      </c>
-      <c r="AC14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD14">
-        <v>2</v>
-      </c>
-      <c r="AE14">
-        <v>3</v>
-      </c>
-      <c r="AF14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14">
-        <v>2</v>
-      </c>
-      <c r="AH14">
-        <v>3</v>
-      </c>
-      <c r="AI14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ14">
-        <v>1</v>
-      </c>
-      <c r="AK14">
-        <v>2</v>
-      </c>
-      <c r="AL14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM14">
-        <v>0</v>
-      </c>
-      <c r="AN14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:40">
-      <c r="A15" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15" t="b">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-      <c r="H15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>2</v>
-      </c>
-      <c r="J15">
-        <v>3</v>
-      </c>
-      <c r="K15" t="b">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>2</v>
-      </c>
-      <c r="M15">
-        <v>3</v>
-      </c>
-      <c r="N15" t="b">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>1</v>
-      </c>
-      <c r="P15">
-        <v>2</v>
-      </c>
-      <c r="Q15" t="b">
-        <v>0</v>
-      </c>
-      <c r="R15">
-        <v>2</v>
-      </c>
-      <c r="S15">
-        <v>4</v>
-      </c>
-      <c r="T15" t="b">
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <v>2</v>
-      </c>
-      <c r="V15">
-        <v>3</v>
-      </c>
-      <c r="W15" t="b">
-        <v>0</v>
-      </c>
-      <c r="X15">
-        <v>2</v>
-      </c>
-      <c r="Y15">
-        <v>4</v>
-      </c>
-      <c r="Z15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA15">
-        <v>1</v>
-      </c>
-      <c r="AB15">
-        <v>2</v>
-      </c>
-      <c r="AC15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD15">
-        <v>2</v>
-      </c>
-      <c r="AE15">
-        <v>3</v>
-      </c>
-      <c r="AF15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15">
-        <v>2</v>
-      </c>
-      <c r="AH15">
-        <v>3</v>
-      </c>
-      <c r="AI15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ15">
-        <v>1</v>
-      </c>
-      <c r="AK15">
-        <v>2</v>
-      </c>
-      <c r="AL15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM15">
-        <v>0</v>
-      </c>
-      <c r="AN15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:40">
-      <c r="A16" t="s">
-        <v>54</v>
-      </c>
-      <c r="B16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" t="s">
-        <v>72</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16" t="b">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16">
-        <v>2</v>
-      </c>
-      <c r="H16" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>2</v>
-      </c>
-      <c r="J16">
-        <v>3</v>
-      </c>
-      <c r="K16" t="b">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>2</v>
-      </c>
-      <c r="M16">
-        <v>3</v>
-      </c>
-      <c r="N16" t="b">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>1</v>
-      </c>
-      <c r="P16">
-        <v>2</v>
-      </c>
-      <c r="Q16" t="b">
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>2</v>
-      </c>
-      <c r="S16">
-        <v>4</v>
-      </c>
-      <c r="T16" t="b">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>2</v>
-      </c>
-      <c r="V16">
-        <v>3</v>
-      </c>
-      <c r="W16" t="b">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>2</v>
-      </c>
-      <c r="Y16">
-        <v>4</v>
-      </c>
-      <c r="Z16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA16">
-        <v>1</v>
-      </c>
-      <c r="AB16">
-        <v>2</v>
-      </c>
-      <c r="AC16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD16">
-        <v>2</v>
-      </c>
-      <c r="AE16">
-        <v>3</v>
-      </c>
-      <c r="AF16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16">
-        <v>2</v>
-      </c>
-      <c r="AH16">
-        <v>3</v>
-      </c>
-      <c r="AI16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ16">
-        <v>1</v>
-      </c>
-      <c r="AK16">
-        <v>2</v>
-      </c>
-      <c r="AL16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM16">
-        <v>0</v>
-      </c>
-      <c r="AN16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:40">
+    <row r="17" spans="1:42">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -2639,6 +2741,12 @@
       </c>
       <c r="AN17">
         <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>28</v>
+      </c>
+      <c r="AP17">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Rules/Colorado Pet Treats Rules Matrix.xlsx
+++ b/Data/Rules/Colorado Pet Treats Rules Matrix.xlsx
@@ -891,10 +891,10 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W3" t="b">
         <v>0</v>
@@ -954,7 +954,7 @@
         <v>52</v>
       </c>
       <c r="AP3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:42">
@@ -2427,10 +2427,10 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W15" t="b">
         <v>0</v>
@@ -2490,7 +2490,7 @@
         <v>42</v>
       </c>
       <c r="AP15">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:42">
